--- a/Result/checksun_type/家庭用紙.xlsx
+++ b/Result/checksun_type/家庭用紙.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>37.83</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>38.31</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>38.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>3869358.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>3871172.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>3871172.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>8979574.0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>5956371.06</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>5956371.06</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-403343.9373719934</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>3869358</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>3869358.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>37.57</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>37.91</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>38.32</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>38.32</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2932934.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>5085370.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>5085370.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>8966073.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>6139245.96</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>6139245.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-248911.3340451708</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2932934</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2932934.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>37.38</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>37.93</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>38.33</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>38.33</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3235720.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>8975058.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>8975058.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>8982585.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>6206365.46</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>6206365.46</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>80927.50406618882</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3235720</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3235720.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>37.33</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>37.97</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>38.34</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>38.34</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>3269719.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>9730531.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>9730531.199999999</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>8809203.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>6279424.88</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>6279424.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>516794.2190800523</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>3269719</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>3269719.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>37.43</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>38.04</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>38.36</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>38.04</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>38.36</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>6048132.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>10499888.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>10499888</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>8611623.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>6343834.52</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>6343834.52</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>1117361.268418428</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>6048132</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>6048132.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>37.59</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>38.39</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>38.39</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>9940349.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>14087975.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>14087975.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>8293851.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>6415232.58</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>6415232.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1637721.329315448</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>9940349</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>9940349.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>37.79</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>38.19</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>38.43</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>38.43</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>22381373.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>12846776.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>12846776.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>7660367.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>6365776.64</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>6365776.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>1905579.547407068</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>22381373</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>22381373.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>37.95</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>38.26</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>38.47</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>38.47</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>7013083.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>8990112.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>8990112.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>6268708.0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>6009271.5</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>6009271.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>887210.8751305575</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>7013083</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>7013083.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>38.01</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>38.3</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>38.48</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>38.48</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>7116503.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>7887875.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>7887875.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>6092590.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>6064102.26</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>6064102.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>1047314.88348088</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>7116503</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>7116503.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>38.02</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>38.32</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>38.5</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>38.32</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>38.5</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>23988569.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>6723359.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>6723359.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>5736961.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>6104545.72</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>6104545.72</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>1227550.078142742</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>23988569</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>23988569.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>38.04</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>38.34</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>38.52</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>38.52</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>3734356.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>2499727.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>2499727.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>3608565.8</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>5703808.76</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>5703808.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-366533.5037025558</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>3734356</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>3734356.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>27.24</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>26.34</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>25.86</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>25.86</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>15398999.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>34221878.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>34221878.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>36617575.1</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>25241855.24</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>25241855.24</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>2053470.207403455</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>15398999</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>15398999.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>27.15</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>26.28</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>25.82</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>31549272.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>38918740.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>38918740.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>36738077.3</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>25462351.56</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>25462351.56</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>4244409.746218462</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>31549272</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>31549272.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>27.09</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>26.21</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>25.79</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>25.79</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>66917706.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>44512832.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>44512832.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>34620079.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>25398329.14</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>25398329.14</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>5492350.917874958</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>66917706</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>66917706.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>27.04</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>26.13</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>25.73</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>25.73</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>38460831.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>40957668.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>40957668.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>29797516.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>24401116.96</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>24401116.96</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>3289493.558888707</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>38460831</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>38460831.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>26.94</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>26.07</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>25.69</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>25.69</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>18782585.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>40170944.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>40170944.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>26760865.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>24094528.78</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>24094528.78</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>3074023.454662319</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>18782585</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>18782585.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>26.83</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>26.04</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>25.66</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>25.66</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>38883310.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>39013271.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>39013271.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>27803305.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>23943921.98</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>23943921.98</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>4764805.968100969</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>38883310</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>38883310.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>26.69</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>26.01</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>25.63</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>25.63</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>59519729.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>34557413.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>34557413.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>25421344.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>23374106.74</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>23374106.74</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>4856388.809866868</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>59519729</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>59519729.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>26.45</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>25.59</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>25.59</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>49141889.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>24727325.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>24727325.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>20699524.6</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>22332782.62</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>22332782.62</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>2602734.090608615</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>49141889</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>49141889.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>26.12</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>25.88</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>25.54</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>25.54</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>34527209.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>18637363.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>18637363.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>17271105.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>21698630.5</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>21698630.5</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>402183.988432236</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>34527209</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>34527209.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>25.93</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>25.84</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>25.5</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>12994221.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>13350786.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>13350786.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>15342192.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>21347314.02</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>21347314.02</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-1189964.157120883</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>12994221</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>12994221.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>25.92000000000001</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>25.48</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>25.48</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>16604021.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>16593340.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>16593340</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>16535240.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>21345209.82</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>21345209.82</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-1114856.930871021</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>16604021</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>16604021.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>18.12</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>17.64</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>17.64</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>6791803.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>10058420.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>10058420.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>20353292.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>15094194.92</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>15094194.92</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-1996695.871977523</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>6791803</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>6791803.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>18.02</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>17.75</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>17.63</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>17.63</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>5688835.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>12748490.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>12748490.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>23731866.1</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>15360881.76</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>15360881.76</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1408807.419375379</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>5688835</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>5688835.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>17.99</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>17.7</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>16688578.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>15079634.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>15079634.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>25532824.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>15494092.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>15494092</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-400477.0792517662</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>16688578</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>16688578.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>18.07</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>11811096.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>17474774.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>17474774.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>25895143.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>15509598.64</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>15509598.64</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-124246.3048161827</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>11811096</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>11811096.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>18.25</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>17.63</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>9311790.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>28417473.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>28417473</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>26672932.2</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>15411366.58</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>15411366.58</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>797393.8124066554</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>9311790</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>9311790.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>18.33</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>20242154.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>30648164.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>30648164.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>26970051.1</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>15411161.88</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>15411161.88</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>2353326.986567616</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>20242154</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>20242154.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>18.4</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>17.58</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>17344555.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>34715241.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>34715241.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>26279480.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>15172436.36</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>15172436.36</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>3320930.842991576</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>17344555</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>17344555.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>18.37</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>17.54</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>28664279.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>35986014.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>35986014.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>26734953.5</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>14965321.98</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>14965321.98</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>4895074.429204676</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>28664279</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>28664279.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>18.17</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>17.48</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>17.6</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>66524587.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>34315511.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>34315511.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>25013118.4</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>14532416.86</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>14532416.86</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>5756199.32275179</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>66524587</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>66524587.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>17.91</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>17.42</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>17.57</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>17.57</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>20465247.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>24928391.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>24928391.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>19851734.8</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>13542466.52</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>13542466.52</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>2724337.623435102</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>20465247</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>20465247.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>17.72</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>17.38</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>17.56</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>17.56</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>40577540.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>23291937.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>23291937.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>18777885.8</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>13347392.76</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>13347392.76</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>3230738.137860011</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>40577540</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>40577540.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/家庭用紙.xlsx
+++ b/Result/checksun_type/家庭用紙.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>78.572</t>
+          <t>68.535</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>42.53</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1163,47 +1163,47 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.89</v>
+        <v>-0.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.75</v>
+        <v>-1.05</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>38.19</t>
+          <t>38.04000000000001</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>38.48</v>
+        <v>38.44</v>
       </c>
       <c r="BA2" t="n">
-        <v>38.27</v>
+        <v>38.25</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>38.38</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-199.96</t>
+          <t>-461.61</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-97.14</t>
+          <t>-98.67</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>17893428.8553719</t>
+          <t>18396323.01639344</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>2979696.0</t>
+          <t>2592211.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>5055240.6</v>
+        <v>5198917</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>3657417.8</t>
+          <t>3647709.3</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>4646947.72</v>
+        <v>4608732.38</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>1397822</t>
+          <t>1551207</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-84903.28583974374</t>
+          <t>-41702.29329257572</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>373550.6060336339</t>
+          <t>195903.1657168483</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>2979696.0</t>
+          <t>2592211.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>215.836</t>
+          <t>78.572</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1650,47 +1650,47 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-1.07</v>
+        <v>-0.89</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.45</v>
+        <v>-0.75</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>38.19</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>38.53</v>
+        <v>38.48</v>
       </c>
       <c r="BA3" t="n">
-        <v>38.29</v>
+        <v>38.27</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-107.88</t>
+          <t>-199.96</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-95.71</t>
+          <t>-97.14</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>17893428.8553719</t>
+          <t>18396323.01639344</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>8249511.0</t>
+          <t>2979696.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>5049355.2</v>
+        <v>5055240.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>3500453.7</t>
+          <t>3657417.8</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>4679024.82</v>
+        <v>4646947.72</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>1548901</t>
+          <t>1397822</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-168258.5389076306</t>
+          <t>-84903.28583974374</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>572475.3205564125</t>
+          <t>373550.6060336339</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>8249511.0</t>
+          <t>2979696.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>230.95</t>
+          <t>215.836</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29.20</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2137,47 +2137,47 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.14</v>
+        <v>-1.07</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.25</v>
+        <v>-0.45</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>38.48999999999999</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>38.58</v>
+        <v>38.53</v>
       </c>
       <c r="BA4" t="n">
-        <v>38.3</v>
+        <v>38.29</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>38.41</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-57.33</t>
+          <t>-107.88</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-94.56</t>
+          <t>-95.71</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>17893428.8553719</t>
+          <t>18396323.01639344</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>8819823.0</t>
+          <t>8249511.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>3806099.8</v>
+        <v>5049355.2</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>2945824.2</t>
+          <t>3500453.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>4628398.48</v>
+        <v>4679024.82</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>860275</t>
+          <t>1548901</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-302937.4224465475</t>
+          <t>-168258.5389076306</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>271584.9012833675</t>
+          <t>572475.3205564125</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>8819823.0</t>
+          <t>8249511.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>87.143</t>
+          <t>230.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>29.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,12 +2605,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2620,18 +2620,18 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.31</v>
+        <v>-1.14</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.02</v>
+        <v>-0.25</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -2641,30 +2641,30 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>38.62</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>38.63</v>
+        <v>38.58</v>
       </c>
       <c r="BA5" t="n">
-        <v>38.31</v>
+        <v>38.3</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.41</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-17.65</t>
+          <t>-57.33</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-93.78</t>
+          <t>-94.55</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>17893428.8553719</t>
+          <t>18396323.01639344</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>3353344.0</t>
+          <t>8819823.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>2358761</v>
+        <v>3806099.8</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>2246925.0</t>
+          <t>2945824.2</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>4483616.76</v>
+        <v>4628398.48</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>111836</t>
+          <t>860275</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-407396.0267610776</t>
+          <t>-302937.4224465475</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-229062.8727239599</t>
+          <t>271584.9012833675</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>3353344.0</t>
+          <t>8819823.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>87.143</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,177 +2911,177 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.72</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-07-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-1.98</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-6.24</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-12-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-07-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>43.2</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>40.5</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-4.20</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025/06/03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2025/07/16</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2025/04/22</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>40.5</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>38.4</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2025-05-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
         <is>
           <t>0.00</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>42.1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2025/07/16</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2025/04/22</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>38.4</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2025-05-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>4.88</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>0.26</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3107,18 +3107,18 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.16</v>
+        <v>-0.31</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.62</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>38.64</v>
+        <v>38.63</v>
       </c>
       <c r="BA6" t="n">
         <v>38.31</v>
@@ -3144,15 +3144,15 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-17.65</t>
         </is>
       </c>
       <c r="BD6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BE6" t="n">
         <v>0.11</v>
       </c>
-      <c r="BE6" t="n">
-        <v>0.12</v>
-      </c>
       <c r="BF6" t="inlineStr">
         <is>
           <t>1.82</t>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-93.50</t>
+          <t>-93.77</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,48 +3170,48 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>17893428.8553719</t>
+          <t>18396323.01639344</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>1873829.0</t>
+          <t>3353344.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>2096501.6</v>
+        <v>2358761</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>2235970.9</t>
+          <t>2246925.0</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>4472035.24</v>
+        <v>4483616.76</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-139469</t>
+          <t>111836</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-439820.236586008</t>
+          <t>-407396.0267610776</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-350398.9829942863</t>
+          <t>-229062.8727239599</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>1873829.0</t>
+          <t>3353344.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>38.4</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
           <t>38.5</t>
-        </is>
-      </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="CS6" t="inlineStr">
-        <is>
-          <t>38.45</t>
-        </is>
-      </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>38.6</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3373,7 +3373,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3383,192 +3383,192 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>48.62</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-6.24</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-07-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>43.2</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>40.5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-4.20</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/06/03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/07/16</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/04/22</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>38.4</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2025-05-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
           <t>0.26</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>76.549</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-2.25</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-12-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-07-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>40.5</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>42.1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/07/16</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/04/22</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>38.4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2025-05-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>7.69</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>0.52</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,47 +3579,47 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>0.03</v>
+        <v>-0.16</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>38.69</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>38.63</v>
+        <v>38.64</v>
       </c>
       <c r="BA7" t="n">
         <v>38.31</v>
@@ -3631,11 +3631,11 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BE7" t="n">
         <v>0.12</v>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-93.41</t>
+          <t>-93.50</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>17893428.8553719</t>
+          <t>18396323.01639344</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>2950269.0</t>
+          <t>1873829.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>2259595</v>
+        <v>2096501.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>2253822.3</t>
+          <t>2235970.9</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>4538894.1</v>
+        <v>4472035.24</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>-139469</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-456078.6463299575</t>
+          <t>-439820.236586008</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-352702.5697020991</t>
+          <t>-350398.9829942863</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>2950269.0</t>
+          <t>1873829.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,164 +3870,164 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>76.549</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-2.25</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-07-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>43.2</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>40.5</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>-0.26</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>52.637</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>-4.20</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025/06/03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2025/07/16</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2025/04/22</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-1.98</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-19.07</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-12-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-07-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>40.5</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>42.1</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2025/07/16</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2025/04/22</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>2025/10/31</t>
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,59 +4066,59 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>69.44</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.28</v>
+        <v>0.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>38.69</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>38.6</v>
+        <v>38.63</v>
       </c>
       <c r="BA8" t="n">
         <v>38.31</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>38.43</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BD8" t="n">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-93.44</t>
+          <t>-93.40</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>17893428.8553719</t>
+          <t>18396323.01639344</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>2033234.0</t>
+          <t>2950269.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>1951552.2</v>
+        <v>2259595</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>2411545.6</t>
+          <t>2253822.3</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>4748225.58</v>
+        <v>4538894.1</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-459993</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-474874.2966259317</t>
+          <t>-456078.6463299575</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-458729.7446524715</t>
+          <t>-352702.5697020991</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>2033234.0</t>
+          <t>2950269.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,42 +4357,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>52.637</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>40.93</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-2.25</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.07</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4452,97 +4452,97 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-4.20</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025/06/03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2025/07/16</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2025/04/22</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>38.4</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2025-05-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>5.28</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
           <t>-0.26</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>42.1</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2025/07/16</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2025/04/22</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>38.4</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>2025-05-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>4.11</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>-0.39</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,50 +4553,50 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.1</v>
+        <v>-0.28</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>38.57</v>
+        <v>38.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>38.3</v>
+        <v>38.31</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -4605,11 +4605,11 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BE9" t="n">
         <v>0.12</v>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-93.50</t>
+          <t>-93.43</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>17893428.8553719</t>
+          <t>18396323.01639344</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>1583129.0</t>
+          <t>2033234.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>2085548.6</v>
+        <v>1951552.2</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>2455629.9</t>
+          <t>2411545.6</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>4801459.22</v>
+        <v>4748225.58</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-370081</t>
+          <t>-459993</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-477809.6697120154</t>
+          <t>-474874.2966259317</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-495560.1822725581</t>
+          <t>-458729.7446524715</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>1583129.0</t>
+          <t>2033234.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
+          <t>38.55</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
           <t>38.6</t>
-        </is>
-      </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>38.7</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>52.68</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-20.35</t>
+          <t>-15.07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
           <t>83.33</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>91.67</t>
-        </is>
-      </c>
       <c r="AU10" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>38.73999999999999</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>38.54</v>
+        <v>38.57</v>
       </c>
       <c r="BA10" t="n">
         <v>38.3</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>38.44</t>
+          <t>38.43</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="BD10" t="n">
         <v>0.14</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-93.74</t>
+          <t>-93.50</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>17893428.8553719</t>
+          <t>18396323.01639344</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>2042047.0</t>
+          <t>1583129.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>2135089</v>
+        <v>2085548.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>2680602.9</t>
+          <t>2455629.9</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>4901156.42</v>
+        <v>4801459.22</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-545513</t>
+          <t>-370081</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-474582.3037919167</t>
+          <t>-477809.6697120154</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-482250.9795058044</t>
+          <t>-495560.1822725581</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>2042047.0</t>
+          <t>1583129.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5284,17 +5284,17 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5321,7 +5321,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1259.573</t>
+          <t>1497.003</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,74 +5346,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>25.65</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>8.07</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>25.95</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>10.45</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>25.95</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>26.0</t>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5501,22 +5501,22 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2023-12-14 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,75 +5527,75 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>56.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-0.61</v>
+        <v>-1.27</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.24</v>
+        <v>-0.09</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26.05</v>
+        <v>26</v>
       </c>
       <c r="BA11" t="n">
-        <v>26.34</v>
+        <v>26.33</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>26.01</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="BE11" t="n">
         <v>-0.17</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-111.52</t>
+          <t>-127.46</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,48 +5605,48 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>130483171.7458678</t>
+          <t>48824914.55840164</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>32841900.0</t>
+          <t>38689106.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>46605430.2</v>
+        <v>42924252.4</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>42197823.7</t>
+          <t>39720688.5</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>27513002.46</v>
+        <v>27997698.18</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>4407606</t>
+          <t>3203563</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>2489480.389758235</t>
+          <t>2495220.423611333</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>3127084.549896255</t>
+          <t>2526790.609803371</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>32841900.0</t>
+          <t>38689106.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2407.159</t>
+          <t>1259.573</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22.64</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5988,22 +5988,22 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2023-12-14 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,59 +6014,59 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>56.25</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0.04</v>
+        <v>-0.61</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.01</v>
+        <v>0.24</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26.09</v>
+        <v>26.05</v>
       </c>
       <c r="BA12" t="n">
         <v>26.34</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.01</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BD12" t="n">
@@ -6077,12 +6077,12 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-111.85</t>
+          <t>-127.48</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,48 +6092,48 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>130483171.7458678</t>
+          <t>48824914.55840164</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>62719914.0</t>
+          <t>32841900.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>51530435.2</v>
+        <v>46605430.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>42017105.6</t>
+          <t>42197823.7</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>27315340.98</v>
+        <v>27513002.46</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>9513329</t>
+          <t>4407606</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>2373552.360642232</t>
+          <t>2489480.389758235</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>4499452.087532654</t>
+          <t>3127084.549896255</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>62719914.0</t>
+          <t>32841900.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
+          <t>26.05</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="CS12" t="inlineStr">
+        <is>
           <t>25.9</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>26.3</t>
-        </is>
-      </c>
-      <c r="CS12" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1443.41</t>
+          <t>2407.159</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.64</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6475,22 +6475,22 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2023-12-14 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,75 +6501,75 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>0.27</v>
+        <v>0.04</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.61</v>
+        <v>-0.01</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>26.14</v>
+        <v>26.09</v>
       </c>
       <c r="BA13" t="n">
         <v>26.34</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="BD13" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="BE13" t="n">
         <v>-0.17</v>
       </c>
-      <c r="BE13" t="n">
-        <v>-0.18</v>
-      </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-112.19</t>
+          <t>-128.28</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>130483171.7458678</t>
+          <t>48824914.55840164</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>37671132.0</t>
+          <t>62719914.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>42199715.6</v>
+        <v>51530435.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>37300439.4</t>
+          <t>42017105.6</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>26208297.38</v>
+        <v>27315340.98</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>4899276</t>
+          <t>9513329</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>1987025.137571245</t>
+          <t>2373552.360642232</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>3098066.638172768</t>
+          <t>4499452.087532654</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>37671132.0</t>
+          <t>62719914.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6782,7 +6782,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1636.865</t>
+          <t>1443.41</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6962,22 +6962,22 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2023-12-14 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>19.36</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,75 +6988,75 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>81.25</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>1.08</v>
+        <v>0.27</v>
       </c>
       <c r="AV14" t="n">
-        <v>-1.25</v>
+        <v>-0.61</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>26.2</v>
+        <v>26.14</v>
       </c>
       <c r="BA14" t="n">
         <v>26.34</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="BE14" t="n">
         <v>-0.18</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-112.28</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>130483171.7458678</t>
+          <t>48824914.55840164</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>42699210.0</t>
+          <t>37671132.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>38771066.6</v>
+        <v>42199715.6</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>36679884.3</t>
+          <t>37300439.4</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>25645213.44</v>
+        <v>26208297.38</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>2091182</t>
+          <t>4899276</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>1785017.592007332</t>
+          <t>1987025.137571245</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>3669240.259152479</t>
+          <t>3098066.638172768</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>42699210.0</t>
+          <t>37671132.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2194.22</t>
+          <t>1636.865</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7449,22 +7449,22 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2023-12-14 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>29.43</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,75 +7475,75 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.25</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>2.18</v>
+        <v>1.08</v>
       </c>
       <c r="AV15" t="n">
-        <v>-1.98</v>
+        <v>-1.25</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>26.26</v>
+        <v>26.2</v>
       </c>
       <c r="BA15" t="n">
         <v>26.34</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-24.24</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-112.09</t>
+          <t>-129.29</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>130483171.7458678</t>
+          <t>48824914.55840164</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>57094995.0</t>
+          <t>42699210.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>36517124.6</v>
+        <v>38771066.6</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>35522699.3</t>
+          <t>36679884.3</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>25114757.3</v>
+        <v>25645213.44</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>994425</t>
+          <t>2091182</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>1442431.652526396</t>
+          <t>1785017.592007332</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>3815435.637010895</t>
+          <t>3669240.259152479</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>57094995.0</t>
+          <t>42699210.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2218.664</t>
+          <t>2194.22</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,149 +7781,149 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>26.3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-2.53</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>25.95</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025/05/28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>27.1</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2025/12/29</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
           <t>25.85</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>12.84</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>2025/06/12</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>27.05</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025/05/28</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2025/12/29</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>25.85</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>2025/06/12</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>27.05</t>
-        </is>
-      </c>
       <c r="AI16" t="inlineStr">
         <is>
           <t>2025/10/30</t>
@@ -7936,22 +7936,22 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2023-12-14 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>29.43</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,75 +7962,75 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="AV16" t="n">
-        <v>-2.82</v>
+        <v>-1.98</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.74</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>26.33</v>
+        <v>26.26</v>
       </c>
       <c r="BA16" t="n">
-        <v>26.33</v>
+        <v>26.34</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-62.29</t>
+          <t>-24.24</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.27</v>
+        <v>-0.22</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-111.36</t>
+          <t>-128.85</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>130483171.7458678</t>
+          <t>48824914.55840164</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>57466925.0</t>
+          <t>57094995.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>37790217.2</v>
+        <v>36517124.6</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>33491472.0</t>
+          <t>35522699.3</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>24623588.3</v>
+        <v>25114757.3</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>4298745</t>
+          <t>994425</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>1010976.382620124</t>
+          <t>1442431.652526396</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>2345615.082629669</t>
+          <t>3815435.637010895</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>57466925.0</t>
+          <t>57094995.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8243,7 +8243,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>626.698</t>
+          <t>2218.664</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -8373,12 +8373,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8423,22 +8423,22 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2023-12-14 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>8.41</t>
+          <t>29.76</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,75 +8449,75 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-0.31</v>
+        <v>1.02</v>
       </c>
       <c r="AV17" t="n">
-        <v>-3</v>
+        <v>-2.82</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>26.42</v>
+        <v>26.33</v>
       </c>
       <c r="BA17" t="n">
-        <v>26.34</v>
+        <v>26.33</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-101.62</t>
+          <t>-62.29</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.14</v>
+        <v>-0.16</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-109.59</t>
+          <t>-127.10</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>130483171.7458678</t>
+          <t>48824914.55840164</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>16066316.0</t>
+          <t>57466925.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>32503776</v>
+        <v>37790217.2</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>30014325.3</t>
+          <t>33491472.0</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>23879234.68</v>
+        <v>24623588.3</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>2489450</t>
+          <t>4298745</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>768314.8008002065</t>
+          <t>1010976.382620124</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>122249.8234197199</t>
+          <t>2345615.082629669</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>16066316.0</t>
+          <t>57466925.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,42 +8740,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>626.698</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>25.55</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>805.534</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8910,22 +8910,22 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2023-12-14 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>8.41</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,75 +8936,75 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-0.78</v>
+        <v>-0.31</v>
       </c>
       <c r="AV18" t="n">
-        <v>-3.06</v>
+        <v>-3</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>26.51</v>
+        <v>26.42</v>
       </c>
       <c r="BA18" t="n">
         <v>26.34</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-152.76</t>
+          <t>-101.62</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.26</v>
+        <v>-0.28</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.1</v>
+        <v>-0.14</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-107.16</t>
+          <t>-122.88</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>130483171.7458678</t>
+          <t>48824914.55840164</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>20527887.0</t>
+          <t>16066316.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>32401163.2</v>
+        <v>32503776</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>29055521.5</t>
+          <t>30014325.3</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>24833364</v>
+        <v>23879234.68</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>3345641</t>
+          <t>2489450</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>885781.1603239313</t>
+          <t>768314.8008002065</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>1377427.209426239</t>
+          <t>122249.8234197199</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>20527887.0</t>
+          <t>16066316.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1233.481</t>
+          <t>805.534</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9397,22 +9397,22 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2023-12-14 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,12 +9423,12 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9438,60 +9438,60 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-1.09</v>
+        <v>-0.78</v>
       </c>
       <c r="AV19" t="n">
         <v>-3.06</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>26.59</v>
+        <v>26.51</v>
       </c>
       <c r="BA19" t="n">
         <v>26.34</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-258.81</t>
+          <t>-152.76</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.23</v>
+        <v>-0.26</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-104.42</t>
+          <t>-117.07</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>130483171.7458678</t>
+          <t>48824914.55840164</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>31429500.0</t>
+          <t>20527887.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>34588702</v>
+        <v>32401163.2</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>28662432.4</t>
+          <t>29055521.5</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>25082203.16</v>
+        <v>24833364</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>5926269</t>
+          <t>3345641</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>796390.9695780571</t>
+          <t>885781.1603239313</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>2643318.467670321</t>
+          <t>1377427.209426239</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>31429500.0</t>
+          <t>20527887.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1202.757</t>
+          <t>998.827</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9884,22 +9884,22 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2023-10-18 00:00:00</t>
+          <t>2025-11-14 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>20.81</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,75 +9910,75 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.64</v>
+        <v>1.34</v>
       </c>
       <c r="AV20" t="n">
-        <v>-2.56</v>
+        <v>-2.19</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>17.22</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>17.66</v>
+        <v>17.6</v>
       </c>
       <c r="BA20" t="n">
-        <v>17.82</v>
+        <v>17.83</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>17.74</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-39.40</t>
+          <t>-20.15</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-117.50</t>
+          <t>-177.63</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>72384578.25</t>
+          <t>32134315.18340164</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>20458420.0</t>
+          <t>17356309.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>20835751.4</v>
+        <v>21127450.4</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>17155195.7</t>
+          <t>17417730.2</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>16289354.1</v>
+        <v>16472776.28</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>3680555</t>
+          <t>3709720</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>338290.342831716</t>
+          <t>490589.313792286</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>1646560.887012478</t>
+          <t>1328233.654075421</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>20458420.0</t>
+          <t>17356309.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,22 +10089,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>61.07</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10159,17 +10159,17 @@
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1877.298</t>
+          <t>1202.757</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10371,22 +10371,22 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2023-10-18 00:00:00</t>
+          <t>2025-11-14 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,75 +10397,75 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-1.62</v>
+        <v>-0.64</v>
       </c>
       <c r="AV21" t="n">
-        <v>-2.55</v>
+        <v>-2.56</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>17.73</v>
+        <v>17.66</v>
       </c>
       <c r="BA21" t="n">
-        <v>17.83</v>
+        <v>17.82</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.74</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-48.47</t>
+          <t>-39.40</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.16</v>
+        <v>-0.18</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-115.78</t>
+          <t>-173.71</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>72384578.25</t>
+          <t>32134315.18340164</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>31992939.0</t>
+          <t>20458420.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>18982966.2</v>
+        <v>20835751.4</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>16211785.8</t>
+          <t>17155195.7</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>16082207.46</v>
+        <v>16289354.1</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>2771180</t>
+          <t>3680555</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>100422.9711624865</t>
+          <t>338290.342831716</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>1710139.295243545</t>
+          <t>1646560.887012478</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>31992939.0</t>
+          <t>20458420.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>61.07</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1056.127</t>
+          <t>1877.298</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,177 +10703,177 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>17.09</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>18.25</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>17.85</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>17.95</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-4.76</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025/07/18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026/01/02</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
           <t>17.25</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>2025/09/02</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>17.85</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>17.25</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>39.11</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
         <is>
           <t>-0.88</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>12.41</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-09-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>18.25</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>17.85</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>17.95</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>17.75</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>-3.36</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025/07/18</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2026/01/02</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>17.25</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>2025/09/02</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>17.7</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>17.85</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>17.25</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>2023-10-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>22.00</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>-0.29</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,12 +10884,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10899,60 +10899,60 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-0.52</v>
+        <v>-1.62</v>
       </c>
       <c r="AV22" t="n">
-        <v>-2.68</v>
+        <v>-2.55</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>17.82</v>
+        <v>17.73</v>
       </c>
       <c r="BA22" t="n">
-        <v>17.84</v>
+        <v>17.83</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>17.76</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-50.33</t>
+          <t>-48.47</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0.21</v>
+        <v>-0.24</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.14</v>
+        <v>-0.16</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-113.87</t>
+          <t>-166.45</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>72384578.25</t>
+          <t>32134315.18340164</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>18239130.0</t>
+          <t>31992939.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>15225594.4</v>
+        <v>18982966.2</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>13544730.1</t>
+          <t>16211785.8</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>15562063.58</v>
+        <v>16082207.46</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>1680864</t>
+          <t>2771180</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-192252.7241249786</t>
+          <t>100422.9711624865</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>504047.8678863682</t>
+          <t>1710139.295243545</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>18239130.0</t>
+          <t>31992939.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>61.07</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11133,17 +11133,17 @@
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11165,7 +11165,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1016.483</t>
+          <t>1056.127</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -11345,22 +11345,22 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2023-10-18 00:00:00</t>
+          <t>2025-11-14 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11386,60 +11386,60 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-0.4</v>
+        <v>-0.52</v>
       </c>
       <c r="AV23" t="n">
-        <v>-2.88</v>
+        <v>-2.68</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>17.89</v>
+        <v>17.82</v>
       </c>
       <c r="BA23" t="n">
         <v>17.84</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.76</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-62.89</t>
+          <t>-50.33</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-112.12</t>
+          <t>-158.40</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>72384578.25</t>
+          <t>32134315.18340164</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>17590454.0</t>
+          <t>18239130.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>14762190.2</v>
+        <v>15225594.4</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>12722030.2</t>
+          <t>13544730.1</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>15382141.84</v>
+        <v>15562063.58</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>2040160</t>
+          <t>1680864</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-318852.8317634054</t>
+          <t>-192252.7241249786</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>236680.7978087477</t>
+          <t>504047.8678863682</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>17590454.0</t>
+          <t>18239130.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>61.07</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>917.883</t>
+          <t>1016.483</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11832,22 +11832,22 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2023-10-18 00:00:00</t>
+          <t>2025-11-14 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,17 +11858,17 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
@@ -11877,28 +11877,28 @@
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>-3.12</v>
+        <v>-2.88</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.37</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>17.96</v>
+        <v>17.89</v>
       </c>
       <c r="BA24" t="n">
         <v>17.84</v>
@@ -11910,23 +11910,23 @@
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-81.60</t>
+          <t>-62.89</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-110.22</t>
+          <t>-151.05</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>72384578.25</t>
+          <t>32134315.18340164</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>15897814.0</t>
+          <t>17590454.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>13708010</v>
+        <v>14762190.2</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>13256934.3</t>
+          <t>12722030.2</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>15298607.9</v>
+        <v>15382141.84</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>451075</t>
+          <t>2040160</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-419858.9462310696</t>
+          <t>-318852.8317634054</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-84224.04508102126</t>
+          <t>236680.7978087477</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>15897814.0</t>
+          <t>17590454.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>61.07</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>641.929</t>
+          <t>917.883</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12319,22 +12319,22 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2023-10-18 00:00:00</t>
+          <t>2025-11-14 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,33 +12345,33 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>-3.23</v>
+        <v>-3.12</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -12381,39 +12381,39 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>18.02</v>
+        <v>17.96</v>
       </c>
       <c r="BA25" t="n">
         <v>17.84</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-118.36</t>
+          <t>-81.60</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="BE25" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-108.13</t>
+          <t>-143.03</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>72384578.25</t>
+          <t>32134315.18340164</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>11194494.0</t>
+          <t>15897814.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>13474640</v>
+        <v>13708010</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>12493283.8</t>
+          <t>13256934.3</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>15287635.14</v>
+        <v>15298607.9</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>981356</t>
+          <t>451075</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-480883.4737128965</t>
+          <t>-419858.9462310696</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-358297.2475992292</t>
+          <t>-84224.04508102126</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>11194494.0</t>
+          <t>15897814.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>61.07</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>761.134</t>
+          <t>641.929</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12806,22 +12806,22 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2023-10-18 00:00:00</t>
+          <t>2025-11-14 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,47 +12832,47 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-0.97</v>
+        <v>0.06</v>
       </c>
       <c r="AV26" t="n">
-        <v>-3.36</v>
+        <v>-3.23</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>18.08</v>
+        <v>18.02</v>
       </c>
       <c r="BA26" t="n">
         <v>17.84</v>
@@ -12884,23 +12884,23 @@
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-196.60</t>
+          <t>-118.36</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="BE26" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-105.73</t>
+          <t>-134.25</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>72384578.25</t>
+          <t>32134315.18340164</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>13206080.0</t>
+          <t>11194494.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>13440605.4</v>
+        <v>13474640</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>12612730.6</t>
+          <t>12493283.8</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>15270668.7</v>
+        <v>15287635.14</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>827874</t>
+          <t>981356</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-503171.878460836</t>
+          <t>-480883.4737128965</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-233106.9209252652</t>
+          <t>-358297.2475992292</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>13206080.0</t>
+          <t>11194494.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>61.07</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CS26" t="inlineStr">
+        <is>
+          <t>17.35</t>
+        </is>
+      </c>
+      <c r="CT26" t="inlineStr">
+        <is>
           <t>17.45</t>
-        </is>
-      </c>
-      <c r="CS26" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="CT26" t="inlineStr">
-        <is>
-          <t>17.3</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>914.735</t>
+          <t>761.134</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13293,22 +13293,22 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2023-10-18 00:00:00</t>
+          <t>2025-11-14 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13338,56 +13338,56 @@
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-0.85</v>
+        <v>-0.97</v>
       </c>
       <c r="AV27" t="n">
-        <v>-3.17</v>
+        <v>-3.36</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>18.12</v>
+        <v>18.08</v>
       </c>
       <c r="BA27" t="n">
-        <v>17.85</v>
+        <v>17.84</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>17.79</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-389.42</t>
+          <t>-196.60</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-0.15</v>
+        <v>-0.17</v>
       </c>
       <c r="BE27" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-102.91</t>
+          <t>-124.11</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>72384578.25</t>
+          <t>32134315.18340164</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>15922109.0</t>
+          <t>13206080.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>11863865.8</v>
+        <v>13440605.4</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>12138842.0</t>
+          <t>12612730.6</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>15210613</v>
+        <v>15270668.7</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-274976</t>
+          <t>827874</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-552274.598012758</t>
+          <t>-503171.878460836</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-261465.4213579837</t>
+          <t>-233106.9209252652</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>15922109.0</t>
+          <t>13206080.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>61.07</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>704.475</t>
+          <t>914.735</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -13645,7 +13645,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-23.82</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13780,22 +13780,22 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2023-10-18 00:00:00</t>
+          <t>2025-11-14 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13825,28 +13825,28 @@
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-1.02</v>
+        <v>-0.85</v>
       </c>
       <c r="AV28" t="n">
-        <v>-2.97</v>
+        <v>-3.17</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>18.17</v>
+        <v>18.12</v>
       </c>
       <c r="BA28" t="n">
         <v>17.85</v>
@@ -13858,23 +13858,23 @@
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-14904.82</t>
+          <t>-389.42</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-0.12</v>
+        <v>-0.15</v>
       </c>
       <c r="BE28" t="n">
-        <v>-0</v>
+        <v>-0.03</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-100.08</t>
+          <t>-112.26</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>72384578.25</t>
+          <t>32134315.18340164</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>12319553.0</t>
+          <t>15922109.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>10681870.2</v>
+        <v>11863865.8</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>14021413.7</t>
+          <t>12138842.0</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>15252955.2</v>
+        <v>15210613</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-3339543</t>
+          <t>-274976</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-605148.9937681715</t>
+          <t>-552274.598012758</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-583642.6212133691</t>
+          <t>-261465.4213579837</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>12319553.0</t>
+          <t>15922109.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>61.07</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>64.48</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CT28" t="inlineStr">
+        <is>
           <t>17.4</t>
-        </is>
-      </c>
-      <c r="CT28" t="inlineStr">
-        <is>
-          <t>17.45</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
